--- a/dapan/cau2.xlsx
+++ b/dapan/cau2.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder (3)\quiz-search\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\cb2604285\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -136,10 +136,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="#,##0\ [$VND]"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -177,36 +178,48 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="8"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -220,102 +233,106 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF00B0F0"/>
+        <color theme="1"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF00B0F0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
-        <color rgb="FF00B0F0"/>
+        <color theme="1"/>
       </right>
       <top style="thin">
-        <color rgb="FF00B0F0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF00B0F0"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF00B0F0"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF00B0F0"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
+        <color theme="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color theme="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color theme="1"/>
       </left>
       <right style="thin">
-        <color rgb="FF00B0F0"/>
+        <color theme="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color theme="1"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
+      <bottom style="dotted">
+        <color theme="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF00B0F0"/>
+        <color theme="1"/>
       </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF00B0F0"/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="dotted">
+        <color theme="1"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="dotted">
+        <color theme="1"/>
+      </top>
       <bottom style="thin">
-        <color rgb="FF00B0F0"/>
+        <color theme="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
       <right style="thin">
-        <color rgb="FF00B0F0"/>
+        <color theme="1"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="hair">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="hair">
+        <color theme="1"/>
+      </top>
+      <bottom style="hair">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="hair">
+        <color theme="1"/>
+      </top>
       <bottom style="thin">
-        <color rgb="FF00B0F0"/>
+        <color theme="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -324,66 +341,53 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -668,100 +672,100 @@
   <dimension ref="A1:H21"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.7265625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="11.453125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="22.26953125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="24.1796875" style="5" customWidth="1"/>
-    <col min="5" max="5" width="17.1796875" style="5" customWidth="1"/>
-    <col min="6" max="6" width="16.453125" style="5" customWidth="1"/>
-    <col min="7" max="7" width="26.26953125" style="5" customWidth="1"/>
-    <col min="8" max="16384" width="9.1796875" style="5"/>
+    <col min="1" max="1" width="5.7265625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="11.453125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="22.26953125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="24.1796875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="17.1796875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="16.453125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="26.26953125" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.1796875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="4"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="6"/>
+      <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
       <c r="D2" s="7"/>
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
-      <c r="G2" s="8"/>
-    </row>
-    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="9"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11" t="s">
+      <c r="G2" s="7"/>
+    </row>
+    <row r="3" spans="1:8" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="10">
         <v>2340000</v>
       </c>
-      <c r="F3" s="10"/>
-      <c r="G3" s="13"/>
-    </row>
-    <row r="4" spans="1:8" s="18" customFormat="1" ht="35" x14ac:dyDescent="0.4">
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+    </row>
+    <row r="4" spans="1:8" s="4" customFormat="1" ht="35" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="17" t="s">
+      <c r="G4" s="14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:8" s="18" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A5" s="19">
+    <row r="5" spans="1:8" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A5" s="16">
         <v>1</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="20" t="str">
+      <c r="D5" s="17" t="str">
         <f>VLOOKUP(LEFT(B5,2),$B$16:$C$20,2,0)</f>
         <v xml:space="preserve">Hiệu trưởng </v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="17">
         <v>8</v>
       </c>
-      <c r="F5" s="21">
+      <c r="F5" s="18">
         <f>IF(LEFT(B5,2)="HT",1000000,IF(LEFT(B5,2)="PH",800000,IF(LEFT(B5,2)="CN",500000,300000)))</f>
         <v>1000000</v>
       </c>
-      <c r="G5" s="22">
+      <c r="G5" s="29">
         <f>(2340000*E5+F5)</f>
         <v>19720000</v>
       </c>
     </row>
-    <row r="6" spans="1:8" s="18" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A6" s="19">
         <v>2</v>
       </c>
@@ -782,12 +786,12 @@
         <f t="shared" ref="F6:F12" si="1">IF(LEFT(B6,2)="HT",1000000,IF(LEFT(B6,2)="PH",800000,IF(LEFT(B6,2)="CN",500000,300000)))</f>
         <v>500000</v>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="30">
         <f t="shared" ref="G6:G12" si="2">(2340000*E6+F6)</f>
         <v>15008000</v>
       </c>
     </row>
-    <row r="7" spans="1:8" s="18" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A7" s="19">
         <v>3</v>
       </c>
@@ -808,12 +812,12 @@
         <f t="shared" si="1"/>
         <v>300000</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="30">
         <f t="shared" si="2"/>
         <v>13872000</v>
       </c>
     </row>
-    <row r="8" spans="1:8" s="18" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A8" s="19">
         <v>4</v>
       </c>
@@ -834,12 +838,12 @@
         <f t="shared" si="1"/>
         <v>800000</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="30">
         <f t="shared" si="2"/>
         <v>18584000</v>
       </c>
     </row>
-    <row r="9" spans="1:8" s="18" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A9" s="19">
         <v>5</v>
       </c>
@@ -860,12 +864,12 @@
         <f t="shared" si="1"/>
         <v>500000</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="30">
         <f t="shared" si="2"/>
         <v>16880000</v>
       </c>
     </row>
-    <row r="10" spans="1:8" s="18" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A10" s="19">
         <v>6</v>
       </c>
@@ -886,12 +890,12 @@
         <f t="shared" si="1"/>
         <v>300000</v>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="30">
         <f t="shared" si="2"/>
         <v>14340000</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="18" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A11" s="19">
         <v>7</v>
       </c>
@@ -912,139 +916,139 @@
         <f t="shared" si="1"/>
         <v>300000</v>
       </c>
-      <c r="G11" s="22">
+      <c r="G11" s="30">
         <f t="shared" si="2"/>
         <v>14340000</v>
       </c>
     </row>
-    <row r="12" spans="1:8" s="18" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A12" s="19">
+    <row r="12" spans="1:8" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A12" s="22">
         <v>8</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="20" t="str">
+      <c r="D12" s="23" t="str">
         <f t="shared" si="0"/>
         <v>Chủ nhiệm bộ môn</v>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="23">
         <v>6.4</v>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="24">
         <f t="shared" si="1"/>
         <v>500000</v>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="31">
         <f t="shared" si="2"/>
         <v>15476000</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="9"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="13"/>
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" s="9"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="13"/>
-    </row>
-    <row r="15" spans="1:8" s="27" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A15" s="23" t="s">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+    </row>
+    <row r="15" spans="1:8" s="6" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A15" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="26"/>
-    </row>
-    <row r="16" spans="1:8" s="27" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A16" s="28"/>
-      <c r="B16" s="29" t="s">
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+    </row>
+    <row r="16" spans="1:8" s="6" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A16" s="13"/>
+      <c r="B16" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="C16" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="26"/>
-    </row>
-    <row r="17" spans="1:7" s="27" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A17" s="28"/>
-      <c r="B17" s="20" t="s">
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+    </row>
+    <row r="17" spans="1:7" s="6" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A17" s="13"/>
+      <c r="B17" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="20" t="s">
+      <c r="C17" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="26"/>
-    </row>
-    <row r="18" spans="1:7" s="27" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A18" s="28"/>
-      <c r="B18" s="20" t="s">
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+    </row>
+    <row r="18" spans="1:7" s="6" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A18" s="13"/>
+      <c r="B18" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="20" t="s">
+      <c r="C18" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="26"/>
-    </row>
-    <row r="19" spans="1:7" s="27" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A19" s="28"/>
-      <c r="B19" s="20" t="s">
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+    </row>
+    <row r="19" spans="1:7" s="6" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A19" s="13"/>
+      <c r="B19" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="20" t="s">
+      <c r="C19" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="26"/>
-    </row>
-    <row r="20" spans="1:7" s="27" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A20" s="28"/>
-      <c r="B20" s="20" t="s">
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+    </row>
+    <row r="20" spans="1:7" s="6" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A20" s="13"/>
+      <c r="B20" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="20" t="s">
+      <c r="C20" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="26"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21" s="30"/>
-      <c r="B21" s="31"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="32"/>
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="2">
